--- a/p6_deployment/data/italy/data_preparation/df_selected.xlsx
+++ b/p6_deployment/data/italy/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,383 +436,508 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_35_segun_loc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_35</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3_segun_loc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>is_rival_match</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4W5t03Zl</t>
+          <t>YH892O2B</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.08725580143589</v>
+        <v>1.926804209993687</v>
       </c>
       <c r="C2" t="n">
-        <v>1.735206305295432</v>
+        <v>0.05018410528920261</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.232941009761241</v>
+        <v>1.746553641984966</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.82912264809646</v>
+        <v>1.762045692695195</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.027870184540236</v>
+        <v>1.65450495508432</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.489611558764191</v>
+        <v>-0.2042154636927389</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4867772163645119</v>
+        <v>-1.549649772445508</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6329865555966449</v>
+        <v>-3.07073149025624</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.03814257833731</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-1.056840118671354</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-1.575138127824429</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-0.920463917082434</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-1.259374028033808</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-1.205192643984268</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.9507057826253159</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.9624141597646952</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-2.82620179011532</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-1.352424657448633</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-1.141146416860645</v>
+        <v>-1.711892956081407</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>-1.322645119749277</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>0.5311225725639235</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>0.6736300804136429</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.692687418675637</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.7233458712745289</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>-1.37229719769782</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>-1.641822704151955</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.2631791669753101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rN4paNle</t>
+          <t>8jyraADG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.08725580143589</v>
+        <v>1.986657396024404</v>
       </c>
       <c r="C3" t="n">
-        <v>1.735206305295432</v>
+        <v>0.09742575393993595</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.232941009761241</v>
+        <v>-0.2708878884913017</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8876692508847811</v>
+        <v>-0.02478357061851841</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.302178900347891</v>
+        <v>1.805660926606482</v>
       </c>
       <c r="G3" t="n">
-        <v>1.06288425710043</v>
+        <v>-0.2042154636927389</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5980052375699849</v>
+        <v>0.4301656404363807</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.18745667723881</v>
+        <v>1.083668243706284</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002765244722242224</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.5150828978731837</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.3413321867191734</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-0.6148543603453704</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-0.4099158850803077</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-0.02846536407245601</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.7053226175015052</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.5407181359181252</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.6156771480250486</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.2303811967568966</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.1957695087490973</v>
+        <v>0.8706391152681163</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="n">
+        <v>-0.2631791669753101</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6Le197C2</t>
+          <t>4xHh663n</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.08725580143589</v>
+        <v>1.926804209993687</v>
       </c>
       <c r="C4" t="n">
-        <v>1.735206305295432</v>
+        <v>-1.414307002883531</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.232941009761241</v>
+        <v>1.320999569150128</v>
       </c>
       <c r="E4" t="n">
-        <v>0.842597453357383</v>
+        <v>1.400156221644316</v>
       </c>
       <c r="F4" t="n">
-        <v>1.268195362590512</v>
+        <v>1.748977437285672</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2178799344968456</v>
+        <v>-0.2042154636927389</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6326303194145283</v>
+        <v>-0.8897113014848786</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6644510065345415</v>
+        <v>0.3912682880458636</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1755384101536995</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.3843570453662051</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.3394733972377884</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.43519732459892</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-0.7288862077050122</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.7758798652343522</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.1323632398341557</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.456017920446496</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-0.8166339336696188</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.401320640685411</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.105964723038405</v>
+        <v>0.4402171033765292</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.3428181824665373</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>0.5635561488950824</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>-0.7159262919236694</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0.3110580569963673</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.2317600808784763</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>0.1730647757462087</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>0.3678094515431893</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.2631791669753101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jPP565dL</t>
+          <t>6RvR2hEi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.08725580143589</v>
+        <v>1.956730803009045</v>
       </c>
       <c r="C5" t="n">
-        <v>1.735206305295432</v>
+        <v>1.27846697020827</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.232941009761241</v>
+        <v>-1.106234772204131</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.521229329793326</v>
+        <v>0.02045261326284142</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.70449835019912</v>
+        <v>-0.4049951569051427</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2920364670742832</v>
+        <v>-0.2042154636927389</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5159628671043508</v>
+        <v>-1.769629262765718</v>
       </c>
       <c r="I5" t="n">
-        <v>1.603889613108888</v>
+        <v>-3.07073149025624</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3442040296309417</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.9591289477445223</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-1.788759184543638</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-2.084058067888778</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.6147581255365355</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-1.503098284468271</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-2.128592808195276</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-1.518286191198811</v>
-      </c>
+        <v>-1.711892956081407</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>-3.169534094818962</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-2.229013044091342</v>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>-1.370485016494856</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>0.8018059957045276</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>-0.3376180686927848</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.9680331559616367</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-1.011891701786494</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>-0.9976428211716513</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>-1.651219116204067</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>3.799692853704542</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4W5t03Zl</t>
+          <t>0lGMiS5j</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.08725580143589</v>
+        <v>1.956730803009045</v>
       </c>
       <c r="C6" t="n">
-        <v>1.735206305295432</v>
+        <v>-0.8946488677254643</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.232941009761241</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>-0.3024104124049934</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.133070075711834</v>
+      </c>
       <c r="F6" t="n">
-        <v>-1.027870184540236</v>
+        <v>-1.444192461120009</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.489611558764191</v>
+        <v>-0.2042154636927389</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4867772163645119</v>
+        <v>2.190001562998059</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6329865555966449</v>
+        <v>-0.3011316676145572</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.03814257833731</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-1.056840118671354</v>
-      </c>
+        <v>0.009795091484941922</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -822,40 +947,75 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.8751409846885709</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>-1.378594780463185</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>0.08096183632134558</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.8422276493354214</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.1606820979649504</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>0.6025329964206113</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>1.447303211240698</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rN4paNle</t>
+          <t>hKOA02XN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.08725580143589</v>
+        <v>1.956730803009045</v>
       </c>
       <c r="C7" t="n">
-        <v>1.735206305295432</v>
+        <v>-1.437927827208898</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.232941009761241</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>-1.200802343945206</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.3640549497287171</v>
+      </c>
       <c r="F7" t="n">
-        <v>-1.302178900347891</v>
+        <v>-1.368614475358928</v>
       </c>
       <c r="G7" t="n">
-        <v>1.06288425710043</v>
+        <v>-0.2042154636927389</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5980052375699849</v>
+        <v>0.2101861501161707</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.18745667723881</v>
+        <v>-0.3011316676145572</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002765244722242224</v>
+        <v>0.009795091484941922</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5150828978731837</v>
+        <v>0.04726979028251885</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -866,41 +1026,74 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>-0.3466555798366531</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>0.2822215877013702</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>-0.1200936203952425</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2340048250415623</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.1806762016294054</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>-0.115601339470829</v>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="n">
+        <v>-0.04654521567571598</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>6Le197C2</t>
+          <t>O2Fteteo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.08725580143589</v>
+        <v>1.926804209993687</v>
       </c>
       <c r="C8" t="n">
-        <v>1.735206305295432</v>
+        <v>0.4044964701697027</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.232941009761241</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>-0.444261770016606</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.400156221644316</v>
+      </c>
       <c r="F8" t="n">
-        <v>1.268195362590512</v>
+        <v>0.7475691259513456</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2178799344968456</v>
+        <v>-0.2042154636927389</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6326303194145283</v>
+        <v>-2.099598498246033</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6644510065345415</v>
+        <v>-1.685931578935399</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1755384101536995</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.3843570453662051</v>
-      </c>
+        <v>-0.8510489322982325</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -910,41 +1103,74 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>-1.890369032401081</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>0.4498140935379459</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>-0.4925712098100786</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.554218967579816</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.8600327190286504</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="n">
+        <v>-1.206984072011519</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="n">
+        <v>-2.380243859896803</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jPP565dL</t>
+          <t>Sf88FVcc</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.08725580143589</v>
+        <v>1.956730803009045</v>
       </c>
       <c r="C9" t="n">
-        <v>1.735206305295432</v>
+        <v>-1.036373813677664</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.232941009761241</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>-0.1132752689228433</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.468010497466356</v>
+      </c>
       <c r="F9" t="n">
-        <v>-1.70449835019912</v>
+        <v>1.484454487121887</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2920364670742832</v>
+        <v>-0.2042154636927389</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5159628671043508</v>
+        <v>-0.4497523208444589</v>
       </c>
       <c r="I9" t="n">
-        <v>1.603889613108888</v>
+        <v>-0.993531623274978</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3442040296309417</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.9591289477445223</v>
-      </c>
+        <v>-0.4206269204066453</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -954,6 +1180,967 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.2096449622898308</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.368283355020666</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.133070075711834</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.1197830853641441</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.3011316676145572</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.009795091484941922</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.160362848581436</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.399805878934358</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9704124747713978</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2101861501161707</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3912682880458636</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4402171033765292</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.2568866109405641</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.16338694958167</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.8390348804829953</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2101861501161707</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9713962539785028</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.510134712632279</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.852518060457915</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1001964049560658</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.036373813677664</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.9742518060995199</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.468010497466356</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3201758952762757</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7588088350502028</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.2708878884913017</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.852518060457915</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2101861501161707</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.083615462328398</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.3496941982755309</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.2962006739066774</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.437927827208898</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.5230680798008351</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.3640549497287171</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.3513699082420308</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.604702284373354</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.9747434321270748</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.4497523208444589</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.225340408280598</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2334724941277653</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.829899968517235</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4044964701697027</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.9959059385062105</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.400156221644316</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3201758952762757</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3912682880458636</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4402171033765292</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.1151616649883641</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.7594870091535229</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.02478357061851841</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1001964049560658</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.727262632390236</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-1.295369915686281</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.852518060457915</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.5934630647726361</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.8855771048082896</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.852518060457915</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.892608402667803</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.699269856114429</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.852518060457915</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.986657396024404</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5698422404472694</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.169279820031515</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.852518060457915</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.805660926606482</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4.896788822537908</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="n">
+        <v>-0.2631791669753101</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/italy/data_preparation/df_selected.xlsx
+++ b/p6_deployment/data/italy/data_preparation/df_selected.xlsx
@@ -425,63 +425,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:AJ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_35_segun_loc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>h2h_35</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3_segun_loc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>is_rival_match</t>
         </is>
       </c>
     </row>
@@ -492,22 +612,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.337142230785994</v>
+        <v>-0.03166292216256539</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1941621238598529</v>
+        <v>-0.9295233270219083</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1298438362837451</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>1.376408122519553</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.796195393244528</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.4719390238590598</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1080439413343977</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>1.506709574191986</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.057752510979272</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.454490572664603</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.4636591014333047</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.469477408737075</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.2998478295005251</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>2.344578442142665</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>1.307977877471829</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.365307411609775</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.939985007505728</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -516,27 +690,79 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.197987040793609</v>
+        <v>0.597121179823038</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1941621238598529</v>
+        <v>-0.7320550162808089</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6889937638985409</v>
+        <v>-1.221164449715159</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02258050492966863</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>-1.476539622822277</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.6356977346409861</v>
+        <v>-0.2580015122135339</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.8754560888496645</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.865645271452597</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>-1.594060428011119</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-1.114955937461657</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-1.042647410196045</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-1.078111313575336</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-1.337222016291918</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-1.51521932539834</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>-1.048389138317659</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="n">
+        <v>-0.8271652973105094</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-1.01766319670494</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-1.360333384784699</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-0.2315504637589359</v>
       </c>
     </row>
     <row r="4">
@@ -546,27 +772,79 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.579352033803153</v>
+        <v>0.296398348438619</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1941621238598529</v>
+        <v>-0.1396500840575105</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.91725016417197</v>
+        <v>1.624583845981469</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.989979370340284</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>-1.560942323501311</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-0.5224575271054814</v>
+        <v>1.767057848486258</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.4719390238590598</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.595912181042843</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1.711566564080417</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-1.973531838519109</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>-1.37670403734278</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-1.505870519487019</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-1.260256056155064</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.3955452079804413</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-1.702859304671268</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.2727392665082766</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>-1.699722513011208</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="n">
+        <v>-1.906963555976704</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-1.942219229658868</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-1.518898477606424</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.2315504637589359</v>
       </c>
     </row>
     <row r="5">
@@ -576,138 +854,424 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.4875049519432741</v>
+        <v>1.553966552409826</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1941621238598529</v>
+        <v>-0.09028300637223562</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5392626363748881</v>
+        <v>-0.4931823275602075</v>
       </c>
       <c r="E5" t="n">
-        <v>1.028860442564645</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+        <v>0.0188051629900348</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5368536386174515</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4731773961295207</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.998364433681231</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>2.03386894596966</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.228489030282725</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.242529536267479</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.1697790321174716</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.751453258318578</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.2890875821933141</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>1.973696713957111</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="n">
+        <v>1.838375569154256</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.470796676271643</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.671448958369514</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>x0nkeyzP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.530910073199722</v>
+        <v>1.88202782301101</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1941621238598529</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+        <v>1.612881173769747</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5160656145182476</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.796195393244528</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>tYhtcc5C</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.852722624751675</v>
+        <v>1.717997187710418</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1941621238598529</v>
+        <v>-0.682687938595534</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.00662909707996923</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+        <v>-0.278096700559881</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3247493829518739</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>-1.192846588745172</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.3937227073864009</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1.694372084878166</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.3398390686099944</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.3904098774050632</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-2.045655775168691</v>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>-1.623362214792423</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="n">
+        <v>-0.3846304610207079</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.3921178780161304</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-1.368279080689855</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>IXMN9zkI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.6328308337535697</v>
+        <v>1.88202782301101</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1941621238598529</v>
+        <v>-1.225725793133557</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1431020304436836</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+        <v>1.574948701289086</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.9573025864120233</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
+          <t>lvG7DIkg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4974815803265078</v>
+        <v>-1.043185173182884</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1941621238598529</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+        <v>1.020476241546449</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8800566755957232</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.082325546666904</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.4719390238590598</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.01366721026397662</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>-1.24107168855711</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.04550386560508141</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.1498079140524505</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.3420426791054583</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.4590116278800004</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.02271559182168639</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.4620892361450358</v>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>0.2100450229045038</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="n">
+        <v>-0.320793793474938</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.2602109327278838</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.5955980068032131</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>SORbFvLt</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.2775897893284026</v>
+        <v>1.553966552409826</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1941621238598529</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+        <v>0.9957927027038115</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.6420877616373566</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.7679085454832657</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.1353783618623509</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.711566564080417</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.973531838519109</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.6809135745258482</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.07494229332378519</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.4503969448279931</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1.321691110250772</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.1002783442785557</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-1.331746001741823</v>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>-0.07910503645351201</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="n">
+        <v>-0.3557775379408495</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.1749907369727604</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.4343955409175518</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -716,27 +1280,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.143374388372266</v>
+        <v>-0.7151239025816996</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1941621238598529</v>
+        <v>-1.694713031143669</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.098412563989684</v>
+        <v>1.177867543750021</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5257204737471569</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>0.4066448907815917</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.3055149549356332</v>
+        <v>1.504819945661825</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.4719390238590598</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.9873564230509713</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5030483883145077</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.06025335679399633</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.5466149668066564</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.6918735768506196</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.987422986104483</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.4384526139747555</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.7019125030265442</v>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0.770424575652867</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="n">
+        <v>0.2809334909386597</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.4346374641054793</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.4473645994685073</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.2315504637589359</v>
       </c>
     </row>
     <row r="12">
@@ -746,27 +1362,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1.343312922603904</v>
+        <v>-0.7698007810152303</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1941621238598529</v>
+        <v>1.143893935759636</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.190196030899398</v>
+        <v>-1.370069883792308</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.989979370340284</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>-1.751126328117048</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-0.8616702905445235</v>
+        <v>0.06251148012744039</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.480731686335571</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-1.961045635837966</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-2.469300025101413</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-1.973531838519109</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-1.341832723728553</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-2.435561256732954</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1.425810261891742</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.4825219298843027</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1.536344221517839</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.7346607563160792</v>
+      </c>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>-1.105772362723517</v>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="n">
+        <v>-1.392928406342616</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.14279303318999</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.7091276902685</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>4.318713008673075</v>
       </c>
     </row>
     <row r="13">
@@ -776,27 +1444,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5197995923455621</v>
+        <v>1.553966552409826</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1941621238598529</v>
+        <v>-1.151675176605645</v>
       </c>
       <c r="D13" t="n">
-        <v>2.722829570194318</v>
+        <v>-0.5262724240217962</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02258050492966863</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>1.142742115831885</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-0.1775096711167878</v>
+        <v>-1.219540489236457</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.563231626046985</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.42055582170351</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.319367280003567</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.9694101458375557</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.834533365154509</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.23027969207405</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.06731795862388987</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.727174368461686</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.5162546324437354</v>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>1.458135513686705</v>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="n">
+        <v>0.8686534851293575</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.120895464403501</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.064174990978612</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0.2315504637589359</v>
       </c>
     </row>
     <row r="14">
@@ -806,27 +1526,81 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.440196843810768</v>
+        <v>-1.207215808483476</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1941621238598529</v>
+        <v>-1.719396569986306</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2663167696474595</v>
+        <v>-1.469340173177074</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02258050492966863</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
-        <v>-0.3429302851392983</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.05573394164776097</v>
+        <v>-0.3017078293509395</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.5368536386174515</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4731773961295207</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.319367280003567</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.007732342947784333</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="n">
+        <v>-1.160900883029566</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.3335178208477537</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.2935061088786799</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.4771482114533748</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.02197276162874637</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.1729020084849273</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.01961552921002626</v>
+      </c>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>-0.6512202079612567</v>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="n">
+        <v>-0.2179138507311957</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.6422347383486182</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0.3478911605035865</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.2315504637589359</v>
       </c>
     </row>
     <row r="15">
@@ -836,20 +1610,80 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.191816348975698</v>
+        <v>-0.1410166790296269</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1941621238598529</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+        <v>1.39072932418601</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.227502688442405</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.5348081874171026</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3514662445311464</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.9538331030594207</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.4875837024189391</v>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.5205183839884103</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.04190105842279478</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.1224571047487803</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.175885645494052</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.004100562789756662</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.7857433804615367</v>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>-0.09807228225123893</v>
+      </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="n">
+        <v>0.306185215236117</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0.142386900315583</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0.298307594095149</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -858,68 +1692,218 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5297762207287957</v>
+        <v>1.88202782301101</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1941621238598529</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+        <v>1.563514096084472</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5491557109798363</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.111463091425174</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.01366721026397662</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>WvwvCQVo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.988071878178737</v>
+        <v>-1.070523612399649</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1941621238598529</v>
+        <v>-0.01623238984432331</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1298438362837451</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+        <v>-0.5759075687141793</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.4995746515014962</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.6736975563543621</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.500511816657474</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.9538331030594207</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-1.478215793152386</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.07347899814445139</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.04555740500660693</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.1304016770863299</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.1372573880846809</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.03575847301530819</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.6886003783729265</v>
+      </c>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="n">
+        <v>-0.3465987322177984</v>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="n">
+        <v>0.08245831935204607</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.2593674088504273</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.239230255234053</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>joLV7EJU</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.5682415529489939</v>
+        <v>-1.425923322217599</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1941621238598529</v>
+        <v>-0.4111690113265222</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1431020304436836</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+        <v>-1.006078822714832</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.219540489236457</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2570895134607253</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>-0.9777898186068252</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.252946152385564</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1624410501358083</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.569403887737849</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.002251181793754789</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.3022790419659659</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.2473255650235831</v>
+      </c>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="n">
+        <v>1.711526653955252</v>
+      </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="n">
+        <v>0.5135726091959627</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.7717834802695496</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.095286519450268</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -928,24 +1912,80 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.3260317499318344</v>
+        <v>0.597121179823038</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1941621238598529</v>
+        <v>-1.29977640966147</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5525208305348266</v>
+        <v>-0.327731845252264</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4805594638878196</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+        <v>-0.9573025864120233</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.500511816657474</v>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>-0.4875837024189391</v>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>-0.4767766758612106</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-1.520330407536874</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.7797522628570988</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.9740292429121971</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.2926629320488925</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-1.179979200710497</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.01456934337076</v>
+      </c>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="n">
+        <v>-1.485591121185128</v>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="n">
+        <v>-1.162663791449353</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-1.21526873849458</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-1.42390272769167</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -954,27 +1994,81 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.6651254741558577</v>
+        <v>1.854689383794245</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1941621238598529</v>
+        <v>0.230602998582051</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.599614830990542</v>
+        <v>-0.6751778580989453</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9836994327053078</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>-2.280682387601594</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-0.9252146205223322</v>
+        <v>1.504819945661825</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.4719390238590598</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2.326179090633089</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.9828997477856625</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="n">
+        <v>-1.524536981738756</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-1.957947969888942</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-2.672611184750323</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1.716365303443057</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.2330187483521263</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-2.544334744077437</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.4913698513283455</v>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="n">
+        <v>-1.98532759637184</v>
+      </c>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="n">
+        <v>-1.297969806307792</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-2.42979455744431</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-2.111253813652432</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-0.2315504637589359</v>
       </c>
     </row>
     <row r="21">
@@ -984,22 +2078,82 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7881333439470991</v>
+        <v>0.6517980582565688</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1941621238598529</v>
+        <v>0.6008560812216125</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2795749638073979</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+        <v>0.8138764826725458</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6161248305345778</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.2141296999117111</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.6222229682558483</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.007732342947784333</v>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>-0.5755041832679223</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.9786744293749099</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.1267535339184163</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.8497852672839931</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.6095679397656607</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.1265958583034184</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.07557580064893113</v>
+      </c>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="n">
+        <v>-0.7508800583680167</v>
+      </c>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="n">
+        <v>-0.02929996702690747</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-0.02755616308562162</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>-0.8682206641014852</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1008,24 +2162,80 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.191816348975698</v>
+        <v>-0.1410166790296269</v>
       </c>
       <c r="C22" t="n">
-        <v>5.150335091728833</v>
+        <v>-0.4111690113265222</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1431020304436836</v>
+        <v>1.227502688442405</v>
       </c>
       <c r="E22" t="n">
-        <v>0.02258050492966863</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+        <v>-1.219540489236457</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.500511816657474</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.007732342947784333</v>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>1.378217101050796</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.1286134746806372</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.059029428254681</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.3799948338570608</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.2898669062028308</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.1477453427598435</v>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="n">
+        <v>1.323914552168133</v>
+      </c>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="n">
+        <v>0.5135726091959627</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.5620472538607415</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.7728412409659323</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1034,24 +2244,80 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.224110989377986</v>
+        <v>1.089213085724815</v>
       </c>
       <c r="C23" t="n">
-        <v>5.150335091728833</v>
+        <v>1.020476241546449</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2663167696474595</v>
+        <v>1.260592784903993</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5257204737471569</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+        <v>1.082325546666904</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.4719390238590598</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3514662445311464</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.998364433681231</v>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.2310425784329029</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2083751586924019</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.136326333969389</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-1.605620309912226</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.139265369351175</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.028252912016008</v>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="n">
+        <v>1.170318327391517</v>
+      </c>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="n">
+        <v>-0.364785149289932</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-0.1224616522644684</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.781552241199433</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1060,22 +2326,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9819011863608267</v>
+        <v>-0.03166292216256539</v>
       </c>
       <c r="C24" t="n">
-        <v>5.150335091728833</v>
+        <v>-0.4605360890117971</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2663167696474595</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+        <v>1.012417061442078</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.8261836349998065</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5368536386174515</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9600220025230181</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>1.163492560860038</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.8610174407965941</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.80729153304311</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.1466402279044475</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.6008770149052359</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.342656632964375</v>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="n">
+        <v>0.9645023265047342</v>
+      </c>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="n">
+        <v>0.3782497398634967</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.5083807169831608</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.662746776584334</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1084,22 +2404,80 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.337142230785994</v>
+        <v>-0.03166292216256539</v>
       </c>
       <c r="C25" t="n">
-        <v>5.150335091728833</v>
+        <v>0.8230079308053494</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1298438362837451</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+        <v>1.376408122519553</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.577663807557501</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.01366721026397662</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.4875837024189391</v>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>-0.3643557986013993</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.1242974591793599</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.3409994254606892</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-0.6582944535325921</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-0.03563688142502698</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.08941808140012512</v>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="n">
+        <v>0.4284926712210184</v>
+      </c>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="n">
+        <v>-0.1959134878484525</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.02534221490781684</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>-0.7611154723269302</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1108,22 +2486,80 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7881333439470991</v>
+        <v>0.6517980582565688</v>
       </c>
       <c r="C26" t="n">
-        <v>5.150335091728833</v>
+        <v>-1.29977640966147</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4027897030111738</v>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+        <v>0.8138764826725458</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.9573025864120233</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.940370703608056</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4731773961295207</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.007732342947784333</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>-0.0348810209427269</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.01823162073242062</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.3103679748912548</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>-0.3067447193509326</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.02511017436888047</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.7094327731466671</v>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="n">
+        <v>0.05918870955975308</v>
+      </c>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="n">
+        <v>0.1986827884800155</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.06624577389347126</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-0.09249511305625589</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1132,22 +2568,80 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4875049519432741</v>
+        <v>1.553966552409826</v>
       </c>
       <c r="C27" t="n">
-        <v>5.150335091728833</v>
+        <v>0.6008560812216125</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2663167696474595</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+        <v>-0.4931823275602075</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.6161248305345778</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1080439413343977</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.1960996420384249</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.4875837024189391</v>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>-0.7805870617969186</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.1439778073025409</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.9515713670072309</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-0.920762505962788</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-0.08278895395244046</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.5562184336485242</v>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="n">
+        <v>-0.4154933571165214</v>
+      </c>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="n">
+        <v>-0.1315511473837191</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-0.02755616308562162</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-0.7754255879299257</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1156,20 +2650,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5682415529489939</v>
+        <v>-1.070523612399649</v>
       </c>
       <c r="C28" t="n">
-        <v>5.150335091728833</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+        <v>-1.349143487346745</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.5759075687141793</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.2580015122135339</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.01366721026397662</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>2.62045997764422</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.66637098927271</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.85297884288999</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.1008351232058463</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.762526612845814</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-0.8278676932381349</v>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="n">
+        <v>2.472247989435678</v>
+      </c>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="n">
+        <v>1.412702465601227</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.374604278954796</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>3.055950481155698</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1178,20 +2728,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.7458620751615775</v>
+        <v>0.1323677131380268</v>
       </c>
       <c r="C29" t="n">
-        <v>5.150335091728833</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>-1.719396569986306</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.757903099252917</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.3017078293509395</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.2701804913637576</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.229755092932772</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>0.8522257299233151</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.2328727300898635</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.309649424906569</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-0.03867411115528279</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.1724205978013726</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.257992512351023</v>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="n">
+        <v>0.8242946793612141</v>
+      </c>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="n">
+        <v>0.3666659922037065</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.04969249089716073</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.009839393935149</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1200,22 +2806,80 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.434026151992858</v>
+        <v>-0.1410166790296269</v>
       </c>
       <c r="C30" t="n">
-        <v>5.150335091728833</v>
+        <v>-0.5592702443823468</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5525208305348266</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+        <v>1.47567841190432</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.190402944478186</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-1.077214621344967</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.9873564230509713</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.9538331030594207</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.007732342947784333</v>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>1.007445240659077</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.01453451169689201</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.6549555324562418</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.6624143949233925</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.08472886193872506</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.427187429679584</v>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="n">
+        <v>0.9683544606544586</v>
+      </c>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="n">
+        <v>0.1995890899368009</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.03551797597587569</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.3979237853784486</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -1224,20 +2888,72 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.02920929449333279</v>
+        <v>-1.207215808483476</v>
       </c>
       <c r="C31" t="n">
-        <v>5.150335091728833</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+        <v>-1.497244720402569</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.03625921582521156</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.796195393244528</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.670066788550652</v>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>1.354841504430557</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.5176154137016409</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.887565094208437</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-0.004174709445832624</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.3521263485339719</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-0.8299227571859908</v>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="n">
+        <v>2.103310849957688</v>
+      </c>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="n">
+        <v>0.4435215895290411</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.3774474942241084</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.224195495921516</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1246,24 +2962,80 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.230281681195897</v>
+        <v>-0.4144010711972805</v>
       </c>
       <c r="C32" t="n">
-        <v>5.150335091728833</v>
+        <v>0.230602998582051</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4027897030111738</v>
+        <v>-1.254254546176747</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5257204737471569</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+        <v>1.504819945661825</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.06842195886845531</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.594888547727895</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5616338189825709</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.5030483883145077</v>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>1.40678041000299</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.4050203490196648</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.969961658737919</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.2666474262638724</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.3079840090402706</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.7189308543510954</v>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="n">
+        <v>1.546637234059704</v>
+      </c>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="n">
+        <v>0.9502244480055813</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.3454444804312421</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.585079791309209</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1272,22 +3044,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.988071878178737</v>
+        <v>-1.425923322217599</v>
       </c>
       <c r="C33" t="n">
-        <v>5.150335091728833</v>
+        <v>-0.3124348559559725</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1298438362837451</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+        <v>-1.006078822714832</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0188051629900348</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.5368536386174515</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4731773961295207</v>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>1.392466000873714</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.3475360161056467</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.757863385955192</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-0.1958016284865624</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.3633859625783723</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.5373900283312593</v>
+      </c>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="n">
+        <v>2.055549381755336</v>
+      </c>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="n">
+        <v>0.3260305269668929</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.3370055518448872</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.416924139369538</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1296,20 +3122,56 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.537080765017632</v>
+        <v>1.88202782301101</v>
       </c>
       <c r="C34" t="n">
-        <v>5.150335091728833</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+        <v>1.612881173769747</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-1.56861046256184</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.796195393244528</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.4719390238590598</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.1353783618623509</v>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1318,20 +3180,56 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.117250439787889</v>
+        <v>1.88202782301101</v>
       </c>
       <c r="C35" t="n">
-        <v>5.150335091728833</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+        <v>0.4280713093231505</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-1.138439208561187</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.796195393244528</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.670066788550652</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.4719390238590598</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.1353783618623509</v>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1340,20 +3238,52 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.530910073199722</v>
+        <v>1.88202782301101</v>
       </c>
       <c r="C36" t="n">
-        <v>5.150335091728833</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+        <v>1.785665945668209</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.574948701289086</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.796195393244528</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.670066788550652</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1362,20 +3292,52 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.40790220340848</v>
+        <v>1.88202782301101</v>
       </c>
       <c r="C37" t="n">
-        <v>5.150335091728833</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+        <v>0.4033877704805131</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-1.436250076715485</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.796195393244528</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.670066788550652</v>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="n">
+        <v>-0.2315504637589359</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/italy/data_preparation/df_selected.xlsx
+++ b/p6_deployment/data/italy/data_preparation/df_selected.xlsx
@@ -728,38 +728,38 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-1.594060428011119</v>
+        <v>-1.595063298652858</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.114955937461657</v>
+        <v>-1.117821908762179</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.042647410196045</v>
+        <v>-1.04782273160451</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.078111313575336</v>
+        <v>-1.063109006551157</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.337222016291918</v>
+        <v>-1.337968621242476</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.51521932539834</v>
+        <v>-1.508405944857024</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>-1.048389138317659</v>
+        <v>-1.068733539813062</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>-0.8271652973105094</v>
+        <v>-0.8336210263200865</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1.01766319670494</v>
+        <v>-1.016927495238437</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.360333384784699</v>
+        <v>-1.37219693748365</v>
       </c>
       <c r="AJ3" t="n">
         <v>-0.2315504637589359</v>
@@ -825,7 +825,7 @@
         <v>-1.702859304671268</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2727392665082766</v>
+        <v>0.2727392665082872</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.88202782301101</v>
+        <v>1.909366262227776</v>
       </c>
       <c r="C6" t="n">
         <v>1.612881173769747</v>
@@ -945,7 +945,7 @@
         <v>0.5160656145182476</v>
       </c>
       <c r="E6" t="n">
-        <v>1.796195393244528</v>
+        <v>1.810764165623664</v>
       </c>
       <c r="F6" t="n">
         <v>-0.2141296999117111</v>
@@ -1035,7 +1035,7 @@
         <v>-0.3904098774050632</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2.045655775168691</v>
+        <v>-2.04565577516867</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.88202782301101</v>
+        <v>1.909366262227776</v>
       </c>
       <c r="C8" t="n">
         <v>-1.225725793133557</v>
@@ -1330,10 +1330,10 @@
         <v>-0.987422986104483</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4384526139747555</v>
+        <v>0.4384526139747554</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.7019125030265442</v>
+        <v>0.7019125030265231</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1346,7 +1346,7 @@
         <v>0.2809334909386597</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.4346374641054793</v>
+        <v>0.4346374641054798</v>
       </c>
       <c r="AI11" t="n">
         <v>0.4473645994685073</v>
@@ -1409,7 +1409,7 @@
         <v>-1.425810261891742</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.4825219298843027</v>
+        <v>-0.4825219298843044</v>
       </c>
       <c r="Z12" t="n">
         <v>-1.536344221517839</v>
@@ -1425,7 +1425,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="n">
-        <v>-1.392928406342616</v>
+        <v>-1.392928406342617</v>
       </c>
       <c r="AH12" t="n">
         <v>-1.14279303318999</v>
@@ -1507,7 +1507,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="n">
-        <v>0.8686534851293575</v>
+        <v>0.8686534851293569</v>
       </c>
       <c r="AH13" t="n">
         <v>1.120895464403501</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.88202782301101</v>
+        <v>1.909366262227776</v>
       </c>
       <c r="C16" t="n">
         <v>1.563514096084472</v>
@@ -1947,41 +1947,41 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="n">
-        <v>-0.4767766758612106</v>
+        <v>-0.4812364164555319</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.520330407536874</v>
+        <v>-1.512367744806085</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7797522628570988</v>
+        <v>-0.7910226127544323</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9740292429121971</v>
+        <v>-0.987250285599252</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.2926629320488925</v>
+        <v>-0.3047998291577966</v>
       </c>
       <c r="Z19" t="n">
-        <v>-1.179979200710497</v>
+        <v>-1.159706555271762</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.01456934337076</v>
+        <v>1.040793936670849</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="n">
-        <v>-1.485591121185128</v>
+        <v>-1.465801455235636</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="n">
-        <v>-1.162663791449353</v>
+        <v>-1.14030843885038</v>
       </c>
       <c r="AH19" t="n">
-        <v>-1.21526873849458</v>
+        <v>-1.243302836481314</v>
       </c>
       <c r="AI19" t="n">
-        <v>-1.42390272769167</v>
+        <v>-1.423326360758929</v>
       </c>
       <c r="AJ19" t="n">
         <v>-0.2315504637589359</v>
@@ -2118,27 +2118,27 @@
         <v>-0.5755041832679223</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9786744293749099</v>
+        <v>-0.9790716416296245</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.1267535339184163</v>
+        <v>-0.1256309870092395</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8497852672839931</v>
+        <v>-0.8444331343407956</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.6095679397656607</v>
+        <v>-0.6123687612647098</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.1265958583034184</v>
+        <v>-0.1267966014662709</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.07557580064893113</v>
+        <v>0.110095177485797</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="n">
-        <v>-0.7508800583680167</v>
+        <v>-0.7620082271933841</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
         <v>-0.02755616308562162</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.8682206641014852</v>
+        <v>-0.8640289045906268</v>
       </c>
       <c r="AJ21" t="n">
         <v>-0.2315504637589359</v>
@@ -2524,27 +2524,27 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>-0.0348810209427269</v>
+        <v>-0.03527823319744144</v>
       </c>
       <c r="W26" t="n">
-        <v>0.01823162073242062</v>
+        <v>0.01935416764159737</v>
       </c>
       <c r="X26" t="n">
-        <v>0.3103679748912548</v>
+        <v>0.3157201078344522</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.3067447193509326</v>
+        <v>-0.3095455408499818</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.02511017436888047</v>
+        <v>0.02490943120602799</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.7094327731466671</v>
+        <v>0.7439521499835329</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="n">
-        <v>0.05918870955975308</v>
+        <v>0.04806054073438568</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
@@ -2555,7 +2555,7 @@
         <v>0.06624577389347126</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.09249511305625589</v>
+        <v>-0.08830335354539735</v>
       </c>
       <c r="AJ26" t="n">
         <v>-0.2315504637589359</v>
@@ -2693,7 +2693,7 @@
         <v>2.85297884288999</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1008351232058463</v>
+        <v>0.100835123205848</v>
       </c>
       <c r="Z28" t="n">
         <v>1.762526612845814</v>
@@ -2774,7 +2774,7 @@
         <v>-0.03867411115528279</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.1724205978013726</v>
+        <v>0.1724205978013725</v>
       </c>
       <c r="AA29" t="n">
         <v>1.257992512351023</v>
@@ -2844,38 +2844,38 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>1.007445240659077</v>
+        <v>0.9852044386583675</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01453451169689201</v>
+        <v>0.01546591483719784</v>
       </c>
       <c r="X30" t="n">
-        <v>0.6549555324562418</v>
+        <v>0.6594173506609315</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.6624143949233925</v>
+        <v>0.6434237407470875</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.08472886193872506</v>
+        <v>0.08135525056178596</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.427187429679584</v>
+        <v>2.422959035158431</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="n">
-        <v>0.9683544606544586</v>
+        <v>0.9484334994766618</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="n">
-        <v>0.1995890899368009</v>
+        <v>0.2069482840561194</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.03551797597587569</v>
+        <v>0.05340561947515715</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.3979237853784486</v>
+        <v>0.3957577385520501</v>
       </c>
       <c r="AJ30" t="n">
         <v>-0.2315504637589359</v>
@@ -3093,7 +3093,7 @@
         <v>0.3633859625783723</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.5373900283312593</v>
+        <v>0.5373900283312382</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.88202782301101</v>
+        <v>1.909366262227776</v>
       </c>
       <c r="C34" t="n">
         <v>1.612881173769747</v>
@@ -3131,7 +3131,7 @@
         <v>-1.56861046256184</v>
       </c>
       <c r="E34" t="n">
-        <v>1.796195393244528</v>
+        <v>1.810764165623664</v>
       </c>
       <c r="F34" t="n">
         <v>4.670066788550652</v>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.88202782301101</v>
+        <v>1.909366262227776</v>
       </c>
       <c r="C35" t="n">
         <v>0.4280713093231505</v>
@@ -3189,7 +3189,7 @@
         <v>-1.138439208561187</v>
       </c>
       <c r="E35" t="n">
-        <v>1.796195393244528</v>
+        <v>1.810764165623664</v>
       </c>
       <c r="F35" t="n">
         <v>4.670066788550652</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.88202782301101</v>
+        <v>1.909366262227776</v>
       </c>
       <c r="C36" t="n">
         <v>1.785665945668209</v>
@@ -3247,7 +3247,7 @@
         <v>1.574948701289086</v>
       </c>
       <c r="E36" t="n">
-        <v>1.796195393244528</v>
+        <v>1.810764165623664</v>
       </c>
       <c r="F36" t="n">
         <v>4.670066788550652</v>
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.88202782301101</v>
+        <v>1.909366262227776</v>
       </c>
       <c r="C37" t="n">
         <v>0.4033877704805131</v>
@@ -3301,7 +3301,7 @@
         <v>-1.436250076715485</v>
       </c>
       <c r="E37" t="n">
-        <v>1.796195393244528</v>
+        <v>1.810764165623664</v>
       </c>
       <c r="F37" t="n">
         <v>4.670066788550652</v>

--- a/p6_deployment/data/italy/data_preparation/df_selected.xlsx
+++ b/p6_deployment/data/italy/data_preparation/df_selected.xlsx
@@ -646,38 +646,38 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>1.506709574191986</v>
+        <v>1.496400322755926</v>
       </c>
       <c r="W2" t="n">
-        <v>2.057752510979272</v>
+        <v>2.090603257987097</v>
       </c>
       <c r="X2" t="n">
-        <v>2.454490572664603</v>
+        <v>2.465246835250709</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.4636591014333047</v>
+        <v>-0.6513708999193901</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.469477408737075</v>
+        <v>1.690680623344347</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2998478295005251</v>
+        <v>0.2058211660090829</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>2.344578442142665</v>
+        <v>2.389563151452224</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>1.307977877471829</v>
+        <v>1.293343516230779</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.365307411609775</v>
+        <v>1.419568621525167</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.939985007505728</v>
+        <v>1.980175996910999</v>
       </c>
       <c r="AJ2" t="n">
         <v>-0.2315504637589359</v>
@@ -728,38 +728,38 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-1.595063298652858</v>
+        <v>-1.622845834245432</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.117821908762179</v>
+        <v>-1.115746573765477</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.04782273160451</v>
+        <v>-0.9744371692785671</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.063109006551157</v>
+        <v>-1.031415896266951</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.337968621242476</v>
+        <v>-1.369493899895923</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.508405944857024</v>
+        <v>-1.262714646354401</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>-1.068733539813062</v>
+        <v>-1.107255153574944</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>-0.8336210263200865</v>
+        <v>-0.7514330917187826</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1.016927495238437</v>
+        <v>-1.045231937113341</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.37219693748365</v>
+        <v>-1.421437091877116</v>
       </c>
       <c r="AJ3" t="n">
         <v>-0.2315504637589359</v>
@@ -810,38 +810,38 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-1.37670403734278</v>
+        <v>-1.468622748059101</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.505870519487019</v>
+        <v>-1.463353857763193</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.260256056155064</v>
+        <v>-1.141359856429053</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3955452079804413</v>
+        <v>0.2548940329298516</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1.702859304671268</v>
+        <v>-1.795861860650786</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2727392665082872</v>
+        <v>-0.009020469897717778</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-1.699722513011208</v>
+        <v>-1.721515159473993</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>-1.906963555976704</v>
+        <v>-2.013691939574219</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1.942219229658868</v>
+        <v>-1.868281232275348</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.518898477606424</v>
+        <v>-1.490401062556848</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0.2315504637589359</v>
@@ -892,38 +892,38 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>2.03386894596966</v>
+        <v>2.049935758784715</v>
       </c>
       <c r="W5" t="n">
-        <v>1.228489030282725</v>
+        <v>1.175718517188405</v>
       </c>
       <c r="X5" t="n">
-        <v>1.242529536267479</v>
+        <v>1.210825099401057</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1697790321174716</v>
+        <v>0.2836103357705774</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.751453258318578</v>
+        <v>1.752191459768925</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2890875821933141</v>
+        <v>0.1115422268398492</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>1.973696713957111</v>
+        <v>1.891872947216038</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>1.838375569154256</v>
+        <v>1.768037889544479</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.470796676271643</v>
+        <v>1.394800005486243</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.671448958369514</v>
+        <v>1.597290275619194</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0.2315504637589359</v>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.909366262227776</v>
+        <v>1.991381579878072</v>
       </c>
       <c r="C6" t="n">
         <v>1.612881173769747</v>
@@ -945,7 +945,7 @@
         <v>0.5160656145182476</v>
       </c>
       <c r="E6" t="n">
-        <v>1.810764165623664</v>
+        <v>1.854470482761069</v>
       </c>
       <c r="F6" t="n">
         <v>-0.2141296999117111</v>
@@ -1020,38 +1020,38 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-1.192846588745172</v>
+        <v>-1.153909280839031</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3937227073864009</v>
+        <v>-0.3476400881078478</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.694372084878166</v>
+        <v>-1.715493670363737</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3398390686099944</v>
+        <v>0.6471816976291758</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.3904098774050632</v>
+        <v>-0.3698361920532552</v>
       </c>
       <c r="AA7" t="n">
-        <v>-2.04565577516867</v>
+        <v>-2.071438247180094</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
-        <v>-1.623362214792423</v>
+        <v>-1.756660447341095</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
-        <v>-0.3846304610207079</v>
+        <v>-0.3512357895383371</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.3921178780161304</v>
+        <v>-0.4446988945926462</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.368279080689855</v>
+        <v>-1.325340052418141</v>
       </c>
       <c r="AJ7" t="n">
         <v>-0.2315504637589359</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.909366262227776</v>
+        <v>1.991381579878072</v>
       </c>
       <c r="C8" t="n">
         <v>-1.225725793133557</v>
@@ -1150,42 +1150,40 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="n">
-        <v>-1.24107168855711</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.04550386560508141</v>
+        <v>-0.2808779997132287</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1498079140524505</v>
+        <v>0.1335881705648471</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3420426791054583</v>
+        <v>0.2385442622696468</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.4590116278800004</v>
+        <v>-0.7036710375825599</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02271559182168639</v>
+        <v>-0.00588397538023413</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4620892361450358</v>
+        <v>0.3294883740769105</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
-        <v>0.2100450229045038</v>
+        <v>-0.1148975252039309</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
-        <v>-0.320793793474938</v>
+        <v>-0.4289678686014315</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.2602109327278838</v>
+        <v>-0.3233081526197025</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.5955980068032131</v>
+        <v>0.5738571070607847</v>
       </c>
       <c r="AJ9" t="n">
         <v>-0.2315504637589359</v>
@@ -1236,38 +1234,38 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.6809135745258482</v>
+        <v>-0.7812628910532985</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.07494229332378519</v>
+        <v>-0.07375151262851086</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4503969448279931</v>
+        <v>-0.4047304621375349</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.321691110250772</v>
+        <v>-1.565569696195364</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.1002783442785557</v>
+        <v>-0.103725394262938</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.331746001741823</v>
+        <v>-1.173437884240805</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>-0.07910503645351201</v>
+        <v>-0.07488210021979289</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
-        <v>-0.3557775379408495</v>
+        <v>-0.3309606938222447</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.1749907369727604</v>
+        <v>-0.192888347194226</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.4343955409175518</v>
+        <v>-0.317671657384758</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0.2315504637589359</v>
@@ -1318,38 +1316,38 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.06025335679399633</v>
+        <v>0.07470380949211698</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5466149668066564</v>
+        <v>0.4629751979494055</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6918735768506196</v>
+        <v>0.5297241878300322</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.987422986104483</v>
+        <v>-1.083601701611451</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4384526139747554</v>
+        <v>0.4383954635426598</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.7019125030265231</v>
+        <v>0.692488846898387</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>0.770424575652867</v>
+        <v>0.8602064643335374</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="n">
-        <v>0.2809334909386597</v>
+        <v>0.2682622957520673</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.4346374641054798</v>
+        <v>0.413864716815992</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.4473645994685073</v>
+        <v>0.3473711009898883</v>
       </c>
       <c r="AJ11" t="n">
         <v>-0.2315504637589359</v>
@@ -1400,38 +1398,38 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>-1.341832723728553</v>
+        <v>-1.249920572238886</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.435561256732954</v>
+        <v>-2.500656814500413</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.425810261891742</v>
+        <v>-1.494643638890997</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.4825219298843044</v>
+        <v>-0.3923545421353806</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.536344221517839</v>
+        <v>-1.597645845610711</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.7346607563160792</v>
+        <v>0.7701268309006439</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
-        <v>-1.105772362723517</v>
+        <v>-1.044626483830037</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="n">
-        <v>-1.392928406342617</v>
+        <v>-1.206961196953795</v>
       </c>
       <c r="AH12" t="n">
-        <v>-1.14279303318999</v>
+        <v>-1.168629137631291</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.7091276902685</v>
+        <v>-1.767161984261072</v>
       </c>
       <c r="AJ12" t="n">
         <v>4.318713008673075</v>
@@ -1482,38 +1480,38 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.9694101458375557</v>
+        <v>0.9389374439651142</v>
       </c>
       <c r="W13" t="n">
-        <v>1.834533365154509</v>
+        <v>1.489797116984839</v>
       </c>
       <c r="X13" t="n">
-        <v>1.23027969207405</v>
+        <v>1.040567755394083</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.06731795862388987</v>
+        <v>-0.3321797946580615</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.727174368461686</v>
+        <v>2.003949726892125</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.5162546324437354</v>
+        <v>0.07213921765189071</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="n">
-        <v>1.458135513686705</v>
+        <v>1.630163470958121</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="n">
-        <v>0.8686534851293569</v>
+        <v>0.7563100725615722</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.120895464403501</v>
+        <v>1.041418067742785</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.064174990978612</v>
+        <v>0.829766936142608</v>
       </c>
       <c r="AJ13" t="n">
         <v>-0.2315504637589359</v>
@@ -1562,42 +1560,40 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="n">
-        <v>-1.160900883029566</v>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-0.3335178208477537</v>
+        <v>-0.3766137411664761</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.2935061088786799</v>
+        <v>-0.2540430802744261</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4771482114533748</v>
+        <v>-0.4124566938475909</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.02197276162874637</v>
+        <v>-0.3188748974479603</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.1729020084849273</v>
+        <v>-0.1597379438978459</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01961552921002626</v>
+        <v>-0.03561617597554163</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>-0.6512202079612567</v>
+        <v>-0.5575411794313563</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="n">
-        <v>-0.2179138507311957</v>
+        <v>-0.4151255053813223</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.6422347383486182</v>
+        <v>-0.6477524993473881</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.3478911605035865</v>
+        <v>-0.2740965442398248</v>
       </c>
       <c r="AJ14" t="n">
         <v>-0.2315504637589359</v>
@@ -1648,38 +1644,38 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5205183839884103</v>
+        <v>0.5351505832434981</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.04190105842279478</v>
+        <v>-0.03979490748691092</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1224571047487803</v>
+        <v>-0.1622642761838027</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.175885645494052</v>
+        <v>1.206778108901433</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.004100562789756662</v>
+        <v>0.001099586282540404</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.7857433804615367</v>
+        <v>-0.9153806707537437</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="n">
-        <v>-0.09807228225123893</v>
+        <v>-0.1509613032172185</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="n">
-        <v>0.306185215236117</v>
+        <v>0.2515837238643533</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.142386900315583</v>
+        <v>-0.2310301686783653</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.298307594095149</v>
+        <v>-0.2643662977205019</v>
       </c>
       <c r="AJ15" t="n">
         <v>-0.2315504637589359</v>
@@ -1692,7 +1688,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.909366262227776</v>
+        <v>1.991381579878072</v>
       </c>
       <c r="C16" t="n">
         <v>1.563514096084472</v>
@@ -1788,38 +1784,38 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.07347899814445139</v>
+        <v>0.2170064161504245</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.04555740500660693</v>
+        <v>-0.05059261825294945</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1304016770863299</v>
+        <v>-0.1822910838396109</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1372573880846809</v>
+        <v>0.3481965764134238</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.03575847301530819</v>
+        <v>-0.02870923935271722</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.6886003783729265</v>
+        <v>0.6165872783961117</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="n">
-        <v>-0.3465987322177984</v>
+        <v>-0.2907812340986174</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
-        <v>0.08245831935204607</v>
+        <v>0.05861614857844481</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.2593674088504273</v>
+        <v>0.277654845303494</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.239230255234053</v>
+        <v>0.078574522356291</v>
       </c>
       <c r="AJ17" t="n">
         <v>-0.2315504637589359</v>
@@ -1864,42 +1860,40 @@
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="n">
-        <v>-0.9777898186068252</v>
-      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>1.252946152385564</v>
+        <v>1.21286255209779</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1624410501358083</v>
+        <v>0.124652250918342</v>
       </c>
       <c r="X18" t="n">
-        <v>1.569403887737849</v>
+        <v>1.435405434311113</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.002251181793754789</v>
+        <v>-0.05661715650242195</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.3022790419659659</v>
+        <v>0.2397906736425315</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.2473255650235831</v>
+        <v>0.163086748523127</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="n">
-        <v>1.711526653955252</v>
+        <v>1.716894708445537</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="n">
-        <v>0.5135726091959627</v>
+        <v>0.4868103131072283</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.7717834802695496</v>
+        <v>0.6066185010396957</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.095286519450268</v>
+        <v>0.9511797117326438</v>
       </c>
       <c r="AJ18" t="n">
         <v>-0.2315504637589359</v>
@@ -1946,42 +1940,40 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="n">
-        <v>-0.4812364164555319</v>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>-1.512367744806085</v>
+        <v>-1.495662880257049</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7910226127544323</v>
+        <v>-0.7907752709024144</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.987250285599252</v>
+        <v>-1.048756624189495</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.3047998291577966</v>
+        <v>-0.04550048763565399</v>
       </c>
       <c r="Z19" t="n">
-        <v>-1.159706555271762</v>
+        <v>-1.161638154939187</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.040793936670849</v>
+        <v>0.9904575147766768</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="n">
-        <v>-1.465801455235636</v>
+        <v>-1.544686088029613</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="n">
-        <v>-1.14030843885038</v>
+        <v>-1.169125075237379</v>
       </c>
       <c r="AH19" t="n">
-        <v>-1.243302836481314</v>
+        <v>-1.092767806413914</v>
       </c>
       <c r="AI19" t="n">
-        <v>-1.423326360758929</v>
+        <v>-1.522542875663299</v>
       </c>
       <c r="AJ19" t="n">
         <v>-0.2315504637589359</v>
@@ -2030,42 +2022,40 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="n">
-        <v>-1.524536981738756</v>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>-1.957947969888942</v>
+        <v>-2.130902766595961</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.672611184750323</v>
+        <v>-2.615539626886055</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.716365303443057</v>
+        <v>-1.734342735704039</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.2330187483521263</v>
+        <v>-0.520534121852428</v>
       </c>
       <c r="Z20" t="n">
-        <v>-2.544334744077437</v>
+        <v>-2.502272193922198</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.4913698513283455</v>
+        <v>0.921182783981265</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="n">
-        <v>-1.98532759637184</v>
+        <v>-2.011809429780987</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="n">
-        <v>-1.297969806307792</v>
+        <v>-1.467577703160486</v>
       </c>
       <c r="AH20" t="n">
-        <v>-2.42979455744431</v>
+        <v>-2.32294473857401</v>
       </c>
       <c r="AI20" t="n">
-        <v>-2.111253813652432</v>
+        <v>-2.185538881189841</v>
       </c>
       <c r="AJ20" t="n">
         <v>-0.2315504637589359</v>
@@ -2114,31 +2104,29 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="n">
-        <v>-0.5755041832679223</v>
-      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>-0.9790716416296245</v>
+        <v>-1.108088087524279</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.1256309870092395</v>
+        <v>-0.1137088213420313</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8444331343407956</v>
+        <v>-0.7940685513874336</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.6123687612647098</v>
+        <v>-0.9867530901272389</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.1267966014662709</v>
+        <v>-0.1329852696603492</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.110095177485797</v>
+        <v>0.07591772950822268</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="n">
-        <v>-0.7620082271933841</v>
+        <v>-0.619459455853097</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
@@ -2149,7 +2137,7 @@
         <v>-0.02755616308562162</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.8640289045906268</v>
+        <v>-0.7238330420091825</v>
       </c>
       <c r="AJ21" t="n">
         <v>-0.2315504637589359</v>
@@ -2200,38 +2188,38 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>1.378217101050796</v>
+        <v>1.273516543404408</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1286134746806372</v>
+        <v>0.08761946074333166</v>
       </c>
       <c r="X22" t="n">
-        <v>1.059029428254681</v>
+        <v>0.9586705639829571</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.3799948338570608</v>
+        <v>0.3849065002042554</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.2898669062028308</v>
+        <v>0.2263405153625745</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.1477453427598435</v>
+        <v>-0.244621106696946</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="n">
-        <v>1.323914552168133</v>
+        <v>1.272927282751588</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="n">
-        <v>0.5135726091959627</v>
+        <v>0.4868103131072283</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.5620472538607415</v>
+        <v>0.403144495446952</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.7728412409659323</v>
+        <v>0.540952834523467</v>
       </c>
       <c r="AJ22" t="n">
         <v>-0.2315504637589359</v>
@@ -2282,38 +2270,38 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2310425784329029</v>
+        <v>0.133846700437054</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2083751586924019</v>
+        <v>0.1926701163797982</v>
       </c>
       <c r="X23" t="n">
-        <v>1.136326333969389</v>
+        <v>1.036127442038615</v>
       </c>
       <c r="Y23" t="n">
-        <v>-1.605620309912226</v>
+        <v>-1.605986959506016</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.139265369351175</v>
+        <v>0.1250636447321454</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.028252912016008</v>
+        <v>0.9983217836589526</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="n">
-        <v>1.170318327391517</v>
+        <v>1.095420142668602</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="n">
-        <v>-0.364785149289932</v>
+        <v>-0.3101836579181683</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.1224616522644684</v>
+        <v>-0.02755616308562162</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.781552241199433</v>
+        <v>0.7209841232493839</v>
       </c>
       <c r="AJ23" t="n">
         <v>-0.2315504637589359</v>
@@ -2360,38 +2348,38 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>1.163492560860038</v>
+        <v>1.161923680103555</v>
       </c>
       <c r="W24" t="n">
-        <v>0.8610174407965941</v>
+        <v>0.9390163981553155</v>
       </c>
       <c r="X24" t="n">
-        <v>1.80729153304311</v>
+        <v>1.927839211935948</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.1466402279044475</v>
+        <v>0.4517952611286653</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.6008770149052359</v>
+        <v>0.4899034463059836</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.342656632964375</v>
+        <v>0.9719848878506487</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="n">
-        <v>0.9645023265047342</v>
+        <v>0.7200011883147402</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="n">
-        <v>0.3782497398634967</v>
+        <v>0.5076242581131015</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.5083807169831608</v>
+        <v>0.4293144476125482</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.662746776584334</v>
+        <v>1.716491451974524</v>
       </c>
       <c r="AJ24" t="n">
         <v>-0.2315504637589359</v>
@@ -2442,38 +2430,38 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>-0.3643557986013993</v>
+        <v>-0.3510339609531953</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1242974591793599</v>
+        <v>-0.1154880341121613</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3409994254606892</v>
+        <v>0.3925760087173585</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.6582944535325921</v>
+        <v>-0.7932606162391754</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.03563688142502698</v>
+        <v>-0.05522879746655593</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.08941808140012512</v>
+        <v>0.1360316521140587</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="n">
-        <v>0.4284926712210184</v>
+        <v>0.6086422939471545</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="n">
-        <v>-0.1959134878484525</v>
+        <v>-0.2370079252137642</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.02534221490781684</v>
+        <v>0.1818735210454771</v>
       </c>
       <c r="AI25" t="n">
-        <v>-0.7611154723269302</v>
+        <v>-0.6696549661805394</v>
       </c>
       <c r="AJ25" t="n">
         <v>-0.2315504637589359</v>
@@ -2524,38 +2512,38 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>-0.03527823319744144</v>
+        <v>-0.05391931179384817</v>
       </c>
       <c r="W26" t="n">
-        <v>0.01935416764159737</v>
+        <v>0.0049276563658999</v>
       </c>
       <c r="X26" t="n">
-        <v>0.3157201078344522</v>
+        <v>0.1937563303813637</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.3095455408499818</v>
+        <v>-0.2131683356077613</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.02490943120602799</v>
+        <v>0.01710127404834046</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.7439521499835329</v>
+        <v>1.006139718077698</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="n">
-        <v>0.04806054073438568</v>
+        <v>0.004911393850210763</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="n">
-        <v>0.1986827884800155</v>
+        <v>0.2315849918636837</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.06624577389347126</v>
+        <v>0.1061313033988671</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.08830335354539735</v>
+        <v>-0.2163906120807883</v>
       </c>
       <c r="AJ26" t="n">
         <v>-0.2315504637589359</v>
@@ -2606,38 +2594,38 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>-0.7805870617969186</v>
+        <v>-0.8525906016566527</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.1439778073025409</v>
+        <v>-0.1352947073790119</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.9515713670072309</v>
+        <v>-0.8483475204178247</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.920762505962788</v>
+        <v>-1.025201807089608</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.08278895395244046</v>
+        <v>-0.08389444689285835</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.5562184336485242</v>
+        <v>0.1086943940875728</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="n">
-        <v>-0.4154933571165214</v>
+        <v>-0.3461294010357787</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="n">
-        <v>-0.1315511473837191</v>
+        <v>-0.1175369471669792</v>
       </c>
       <c r="AH27" t="n">
         <v>-0.02755616308562162</v>
       </c>
       <c r="AI27" t="n">
-        <v>-0.7754255879299257</v>
+        <v>-0.6240977458293089</v>
       </c>
       <c r="AJ27" t="n">
         <v>-0.2315504637589359</v>
@@ -2684,38 +2672,38 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>2.62045997764422</v>
+        <v>2.665938848453598</v>
       </c>
       <c r="W28" t="n">
-        <v>2.66637098927271</v>
+        <v>2.710338507098338</v>
       </c>
       <c r="X28" t="n">
-        <v>2.85297884288999</v>
+        <v>2.842431350165445</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.100835123205848</v>
+        <v>0.1859227884261737</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.762526612845814</v>
+        <v>1.844640824284886</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.8278676932381349</v>
+        <v>-1.005267394581133</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="n">
-        <v>2.472247989435678</v>
+        <v>2.488706026382861</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="n">
-        <v>1.412702465601227</v>
+        <v>1.260555558236114</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.374604278954796</v>
+        <v>1.356298295405935</v>
       </c>
       <c r="AI28" t="n">
-        <v>3.055950481155698</v>
+        <v>2.912031790143133</v>
       </c>
       <c r="AJ28" t="n">
         <v>-0.2315504637589359</v>
@@ -2762,38 +2750,38 @@
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0.8522257299233151</v>
+        <v>0.882953639704771</v>
       </c>
       <c r="W29" t="n">
-        <v>0.2328727300898635</v>
+        <v>0.2274869386033002</v>
       </c>
       <c r="X29" t="n">
-        <v>1.309649424906569</v>
+        <v>1.327486363677788</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.03867411115528279</v>
+        <v>-0.3400164933624907</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.1724205978013725</v>
+        <v>0.2062360025596782</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.257992512351023</v>
+        <v>0.9779423162017148</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="n">
-        <v>0.8242946793612141</v>
+        <v>1.093226843950578</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="n">
-        <v>0.3666659922037065</v>
+        <v>0.2980917728764793</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.04969249089716073</v>
+        <v>0.03865696889962052</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.009839393935149</v>
+        <v>1.034494799408063</v>
       </c>
       <c r="AJ29" t="n">
         <v>-0.2315504637589359</v>
@@ -2844,38 +2832,38 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>0.9852044386583675</v>
+        <v>1.125078760231576</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01546591483719784</v>
+        <v>0.02712555065140831</v>
       </c>
       <c r="X30" t="n">
-        <v>0.6594173506609315</v>
+        <v>0.6374206422988038</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.6434237407470875</v>
+        <v>0.9832267941496156</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.08135525056178596</v>
+        <v>0.08260285821259347</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.422959035158431</v>
+        <v>2.566708966901738</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="n">
-        <v>0.9484334994766618</v>
+        <v>0.9109008297567326</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="n">
-        <v>0.2069482840561194</v>
+        <v>0.2723607597684297</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.05340561947515715</v>
+        <v>0.1377760210229828</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.3957577385520501</v>
+        <v>0.3215316792935797</v>
       </c>
       <c r="AJ30" t="n">
         <v>-0.2315504637589359</v>
@@ -2918,38 +2906,38 @@
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>1.354841504430557</v>
+        <v>1.398459757923407</v>
       </c>
       <c r="W31" t="n">
-        <v>0.5176154137016409</v>
+        <v>0.4716190514642747</v>
       </c>
       <c r="X31" t="n">
-        <v>1.887565094208437</v>
+        <v>1.766781653216937</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.004174709445832624</v>
+        <v>0.1448260002789079</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.3521263485339719</v>
+        <v>0.3645607813971276</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.8299227571859908</v>
+        <v>-1.074192660610044</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="n">
-        <v>2.103310849957688</v>
+        <v>2.141628864298663</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="n">
-        <v>0.4435215895290411</v>
+        <v>0.5960011956255418</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.3774474942241084</v>
+        <v>0.3536422967722714</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.224195495921516</v>
+        <v>1.180036058003137</v>
       </c>
       <c r="AJ31" t="n">
         <v>-0.2315504637589359</v>
@@ -3000,38 +2988,38 @@
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
-        <v>1.40678041000299</v>
+        <v>1.292114858726301</v>
       </c>
       <c r="W32" t="n">
-        <v>0.4050203490196648</v>
+        <v>0.3632914487180789</v>
       </c>
       <c r="X32" t="n">
-        <v>1.969961658737919</v>
+        <v>1.994884917099731</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.2666474262638724</v>
+        <v>0.1024741093776278</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.3079840090402706</v>
+        <v>0.2619299972042452</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.7189308543510954</v>
+        <v>0.9489676892854951</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="n">
-        <v>1.546637234059704</v>
+        <v>1.539929781154423</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="n">
-        <v>0.9502244480055813</v>
+        <v>0.781445221139121</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.3454444804312421</v>
+        <v>0.3586871068282901</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.585079791309209</v>
+        <v>1.545933622912971</v>
       </c>
       <c r="AJ32" t="n">
         <v>-0.2315504637589359</v>
@@ -3078,38 +3066,38 @@
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
-        <v>1.392466000873714</v>
+        <v>1.411520178269538</v>
       </c>
       <c r="W33" t="n">
-        <v>0.3475360161056467</v>
+        <v>0.2962552225722602</v>
       </c>
       <c r="X33" t="n">
-        <v>1.757863385955192</v>
+        <v>1.587366187480087</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.1958016284865624</v>
+        <v>-0.3534298961035779</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.3633859625783723</v>
+        <v>0.3395123023563117</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.5373900283312382</v>
+        <v>0.6296965642966124</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="n">
-        <v>2.055549381755336</v>
+        <v>2.072795838996226</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="n">
-        <v>0.3260305269668929</v>
+        <v>0.2926358554845221</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.3370055518448872</v>
+        <v>0.3895865684214029</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.416924139369538</v>
+        <v>1.39555133951693</v>
       </c>
       <c r="AJ33" t="n">
         <v>-0.2315504637589359</v>
@@ -3118,29 +3106,29 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.909366262227776</v>
+        <v>1.991381579878072</v>
       </c>
       <c r="C34" t="n">
-        <v>1.612881173769747</v>
+        <v>-1.052941021235096</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.56861046256184</v>
+        <v>0.5491557109798363</v>
       </c>
       <c r="E34" t="n">
-        <v>1.810764165623664</v>
+        <v>1.854470482761069</v>
       </c>
       <c r="F34" t="n">
         <v>4.670066788550652</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.4719390238590598</v>
+        <v>-0.2701804913637576</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1353783618623509</v>
+        <v>0.1080439413343977</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -3176,20 +3164,20 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.909366262227776</v>
+        <v>1.991381579878072</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4280713093231505</v>
+        <v>1.612881173769747</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.138439208561187</v>
+        <v>-1.56861046256184</v>
       </c>
       <c r="E35" t="n">
-        <v>1.810764165623664</v>
+        <v>1.854470482761069</v>
       </c>
       <c r="F35" t="n">
         <v>4.670066788550652</v>
@@ -3238,7 +3226,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.909366262227776</v>
+        <v>1.991381579878072</v>
       </c>
       <c r="C36" t="n">
         <v>1.785665945668209</v>
@@ -3247,7 +3235,7 @@
         <v>1.574948701289086</v>
       </c>
       <c r="E36" t="n">
-        <v>1.810764165623664</v>
+        <v>1.854470482761069</v>
       </c>
       <c r="F36" t="n">
         <v>4.670066788550652</v>
@@ -3292,7 +3280,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.909366262227776</v>
+        <v>1.991381579878072</v>
       </c>
       <c r="C37" t="n">
         <v>0.4033877704805131</v>
@@ -3301,7 +3289,7 @@
         <v>-1.436250076715485</v>
       </c>
       <c r="E37" t="n">
-        <v>1.810764165623664</v>
+        <v>1.854470482761069</v>
       </c>
       <c r="F37" t="n">
         <v>4.670066788550652</v>
